--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
@@ -36,22 +36,31 @@
     <t xml:space="preserve">Biobío</t>
   </si>
   <si>
+    <t xml:space="preserve">Negrete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Juana</t>
+  </si>
+  <si>
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
     <t xml:space="preserve">Quilaco</t>
   </si>
   <si>
-    <t xml:space="preserve">Negrete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Juana</t>
+    <t xml:space="preserve">Hualqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">Tucapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Hualqui</t>
+    <t xml:space="preserve">Hualpén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Bárbara</t>
   </si>
   <si>
     <t xml:space="preserve">Los Alamos</t>
@@ -60,81 +69,72 @@
     <t xml:space="preserve">Contulmo</t>
   </si>
   <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yumbel</t>
   </si>
   <si>
+    <t xml:space="preserve">Cabrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curanilahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilleco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirúa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cañete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Antuco</t>
   </si>
   <si>
-    <t xml:space="preserve">Quilleco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Biobío</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mulchén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cañete</t>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Angeles</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
   </si>
   <si>
-    <t xml:space="preserve">Santa Bárbara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirúa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronel</t>
+    <t xml:space="preserve">Lota</t>
   </si>
   <si>
     <t xml:space="preserve">Concepción</t>
   </si>
   <si>
-    <t xml:space="preserve">Curanilahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lebu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nacimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiguayante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualpén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:52</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -574,13 +574,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>8104</v>
+        <v>8307</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.03</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="3">
@@ -591,13 +591,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8308</v>
+        <v>8109</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14.03</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="4">
@@ -608,13 +608,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8307</v>
+        <v>8104</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>9.47</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="5">
@@ -625,13 +625,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8109</v>
+        <v>8308</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9.19</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="6">
@@ -642,13 +642,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8312</v>
+        <v>8105</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8.73</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="7">
@@ -659,13 +659,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8105</v>
+        <v>8314</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8.5</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="8">
@@ -676,13 +676,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>8206</v>
+        <v>8312</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7.84</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="9">
@@ -693,13 +693,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>8204</v>
+        <v>8112</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>7.39</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="10">
@@ -710,13 +710,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8313</v>
+        <v>8311</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6.75</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -727,13 +727,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>8302</v>
+        <v>8206</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5.58</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="12">
@@ -744,13 +744,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>8309</v>
+        <v>8204</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.36</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="13">
@@ -761,13 +761,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>8303</v>
+        <v>8310</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.96</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="14">
@@ -778,13 +778,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>8314</v>
+        <v>8304</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3.94</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="15">
@@ -795,13 +795,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>8305</v>
+        <v>8313</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.88</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="16">
@@ -812,13 +812,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8203</v>
+        <v>8303</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.71</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="17">
@@ -829,13 +829,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>8108</v>
+        <v>8305</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.59</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="18">
@@ -846,13 +846,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>8311</v>
+        <v>8103</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.09</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="19">
@@ -863,13 +863,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>8304</v>
+        <v>8205</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="20">
@@ -880,13 +880,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>8310</v>
+        <v>8309</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.78</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="21">
@@ -897,13 +897,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>8202</v>
+        <v>8107</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.48</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="22">
@@ -914,13 +914,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8301</v>
+        <v>8207</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.48</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="23">
@@ -931,13 +931,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8111</v>
+        <v>8202</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.47</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="24">
@@ -948,13 +948,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>8207</v>
+        <v>8203</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.14</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="25">
@@ -965,13 +965,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>8102</v>
+        <v>8111</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.06</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="26">
@@ -982,13 +982,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>8101</v>
+        <v>8306</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="27">
@@ -999,13 +999,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8205</v>
+        <v>8102</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="28">
@@ -1016,13 +1016,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>8201</v>
+        <v>8302</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.54</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="29">
@@ -1033,13 +1033,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>8306</v>
+        <v>8201</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-1.06</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="30">
@@ -1050,13 +1050,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>8103</v>
+        <v>8301</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-1.65</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="31">
@@ -1067,13 +1067,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>8112</v>
+        <v>8108</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-2.23</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="32">
@@ -1084,13 +1084,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-2.34</v>
+        <v>-0.69</v>
       </c>
     </row>
     <row r="33">
@@ -1101,13 +1101,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8110</v>
+        <v>8101</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-4.89</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="34">
@@ -1118,13 +1118,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>8106</v>
+        <v>8110</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-6.1</v>
+        <v>-2.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -580,7 +580,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.29</v>
+        <v>62.87</v>
       </c>
     </row>
     <row r="3">
@@ -597,7 +597,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.82</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="4">
@@ -614,7 +614,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.71</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="5">
@@ -631,7 +631,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.44</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="6">
@@ -648,7 +648,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.94</v>
+        <v>29.39</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.87</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="8">
@@ -682,7 +682,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.64</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="9">
@@ -699,7 +699,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.36</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2.1</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.05</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="12">
@@ -750,7 +750,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.93</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="13">
@@ -767,7 +767,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.68</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="14">
@@ -784,7 +784,7 @@
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.59</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="15">
@@ -801,7 +801,7 @@
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.35</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="16">
@@ -818,7 +818,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.31</v>
+        <v>13.14</v>
       </c>
     </row>
     <row r="17">
@@ -835,7 +835,7 @@
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.29</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="18">
@@ -852,7 +852,7 @@
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.28</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="19">
@@ -869,7 +869,7 @@
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.22</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="20">
@@ -886,7 +886,7 @@
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.13</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="21">
@@ -903,7 +903,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.84</v>
+        <v>8.36</v>
       </c>
     </row>
     <row r="22">
@@ -920,7 +920,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.62</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="23">
@@ -937,7 +937,7 @@
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.46</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="24">
@@ -954,7 +954,7 @@
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.39</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.3</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="26">
@@ -988,7 +988,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="27">
@@ -1005,7 +1005,7 @@
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.08</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="28">
@@ -1022,7 +1022,7 @@
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="29">
@@ -1039,7 +1039,7 @@
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-0.12</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="30">
@@ -1056,7 +1056,7 @@
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.24</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="31">
@@ -1073,7 +1073,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.52</v>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="32">
@@ -1090,7 +1090,7 @@
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.69</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="33">
@@ -1107,7 +1107,7 @@
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-1.42</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="34">
@@ -1124,7 +1124,7 @@
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-2.58</v>
+        <v>-25.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Santa Bárbara</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Contulmo</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">San Pedro de la Paz</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:28</t>
+    <t xml:space="preserve">2026-10-04 08:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:17</t>
+    <t xml:space="preserve">2026-10-05 08:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
